--- a/Data/ID_Generators/CZECHIA_IDGenerator.xlsx
+++ b/Data/ID_Generators/CZECHIA_IDGenerator.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA9110A-2EF4-43F9-924E-D745181246BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78BCA64-7114-4F78-9BE3-E00F151BFFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5300,7 +5300,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C159E3-9686-4598-8355-985D37798D7D}">
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="L88" cm="1">
         <f t="array" aca="1" ref="L88:L102" ca="1">_xlfn.RANDARRAY(15,1,123456789,999999999,TRUE)</f>
-        <v>394175226</v>
+        <v>399751886</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="L89">
         <f ca="1"/>
-        <v>241922435</v>
+        <v>290771024</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="L90">
         <f ca="1"/>
-        <v>658728657</v>
+        <v>856684449</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="L91">
         <f ca="1"/>
-        <v>487374245</v>
+        <v>574057338</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="L92">
         <f ca="1"/>
-        <v>157402347</v>
+        <v>416157219</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="L93">
         <f ca="1"/>
-        <v>918571278</v>
+        <v>309890258</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="L94">
         <f ca="1"/>
-        <v>887440803</v>
+        <v>999678488</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="L95">
         <f ca="1"/>
-        <v>190325973</v>
+        <v>428803409</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="L96">
         <f ca="1"/>
-        <v>733254577</v>
+        <v>405246983</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="L97">
         <f ca="1"/>
-        <v>866496163</v>
+        <v>431872517</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="L98">
         <f ca="1"/>
-        <v>288485373</v>
+        <v>487214015</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="L99">
         <f ca="1"/>
-        <v>940248216</v>
+        <v>561806619</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="L100">
         <f ca="1"/>
-        <v>671980592</v>
+        <v>899676195</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="L101">
         <f ca="1"/>
-        <v>362092306</v>
+        <v>896904081</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L102">
         <f ca="1"/>
-        <v>602443598</v>
+        <v>460808035</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -6425,6 +6425,151 @@
     <row r="212" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A212" s="19">
         <v>141853012</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A213" s="19">
+        <v>141843013</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A214" s="19">
+        <v>141833014</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A215" s="19">
+        <v>141823015</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A216" s="19">
+        <v>141813016</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A217" s="19">
+        <v>141803017</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A218" s="19">
+        <v>141793018</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A219" s="19">
+        <v>141783019</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A220" s="19">
+        <v>141773020</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A221" s="19">
+        <v>141763021</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A222" s="19">
+        <v>141753022</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A223" s="19">
+        <v>141743023</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A224" s="19">
+        <v>141733024</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A225" s="19">
+        <v>141723025</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A226" s="19">
+        <v>141713026</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A227" s="19">
+        <v>141703027</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A228" s="19">
+        <v>141693028</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A229" s="19">
+        <v>141683029</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A230" s="19">
+        <v>141673030</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A231" s="19">
+        <v>141663031</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A232" s="19">
+        <v>141653032</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A233" s="19">
+        <v>141643033</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A234" s="19">
+        <v>141633034</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A235" s="19">
+        <v>141623035</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A236" s="19">
+        <v>141613036</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A237" s="19">
+        <v>141603037</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A238" s="19">
+        <v>141593038</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A239" s="19">
+        <v>141583039</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A240" s="19">
+        <v>141573040</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A241" s="19">
+        <v>141563041</v>
       </c>
     </row>
   </sheetData>
